--- a/docs/Analytic Hierarchy Process.xlsx
+++ b/docs/Analytic Hierarchy Process.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\scalere1\OneDrive - Tallinna Tehnikaülikool\Documents\GitHub\AHP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://livettu-my.sharepoint.com/personal/edoard_taltech_ee/Documents/Documents/GitHub/AHP/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4723CE8A-F51E-4639-A243-7086AF122F3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4305" yWindow="2550" windowWidth="29835" windowHeight="17310" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="7965" yWindow="480" windowWidth="25605" windowHeight="15570" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AHP sample" sheetId="1" r:id="rId1"/>
@@ -698,7 +698,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -750,22 +750,14 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -3691,121 +3683,121 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:46" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="L1" s="35" t="s">
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="L1" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="M1" s="35"/>
-      <c r="N1" s="35"/>
-      <c r="O1" s="35"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
       <c r="R1" s="6"/>
       <c r="S1" s="6"/>
       <c r="T1" s="5"/>
       <c r="U1" s="5"/>
-      <c r="V1" s="35" t="s">
+      <c r="V1" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="W1" s="35"/>
-      <c r="X1" s="35"/>
-      <c r="Y1" s="35"/>
-      <c r="AF1" s="35" t="s">
+      <c r="W1" s="34"/>
+      <c r="X1" s="34"/>
+      <c r="Y1" s="34"/>
+      <c r="AF1" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="AG1" s="35"/>
-      <c r="AH1" s="35"/>
-      <c r="AK1" s="35" t="s">
+      <c r="AG1" s="34"/>
+      <c r="AH1" s="34"/>
+      <c r="AK1" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="AL1" s="35"/>
-      <c r="AM1" s="35"/>
-      <c r="AN1" s="35"/>
-      <c r="AO1" s="35"/>
+      <c r="AL1" s="34"/>
+      <c r="AM1" s="34"/>
+      <c r="AN1" s="34"/>
+      <c r="AO1" s="34"/>
     </row>
     <row r="2" spans="1:46" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="35"/>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="L2" s="35"/>
-      <c r="M2" s="35"/>
-      <c r="N2" s="35"/>
-      <c r="O2" s="35"/>
+      <c r="A2" s="34"/>
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="L2" s="34"/>
+      <c r="M2" s="34"/>
+      <c r="N2" s="34"/>
+      <c r="O2" s="34"/>
       <c r="Q2" s="6"/>
       <c r="R2" s="6"/>
       <c r="S2" s="6"/>
       <c r="T2" s="5"/>
       <c r="U2" s="5"/>
-      <c r="V2" s="35"/>
-      <c r="W2" s="35"/>
-      <c r="X2" s="35"/>
-      <c r="Y2" s="35"/>
-      <c r="AF2" s="35"/>
-      <c r="AG2" s="35"/>
-      <c r="AH2" s="35"/>
-      <c r="AK2" s="35"/>
-      <c r="AL2" s="35"/>
-      <c r="AM2" s="35"/>
-      <c r="AN2" s="35"/>
-      <c r="AO2" s="35"/>
+      <c r="V2" s="34"/>
+      <c r="W2" s="34"/>
+      <c r="X2" s="34"/>
+      <c r="Y2" s="34"/>
+      <c r="AF2" s="34"/>
+      <c r="AG2" s="34"/>
+      <c r="AH2" s="34"/>
+      <c r="AK2" s="34"/>
+      <c r="AL2" s="34"/>
+      <c r="AM2" s="34"/>
+      <c r="AN2" s="34"/>
+      <c r="AO2" s="34"/>
     </row>
     <row r="3" spans="1:46" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="35"/>
-      <c r="B3" s="35"/>
-      <c r="C3" s="35"/>
-      <c r="D3" s="35"/>
-      <c r="L3" s="35"/>
-      <c r="M3" s="35"/>
-      <c r="N3" s="35"/>
-      <c r="O3" s="35"/>
+      <c r="A3" s="34"/>
+      <c r="B3" s="34"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
+      <c r="L3" s="34"/>
+      <c r="M3" s="34"/>
+      <c r="N3" s="34"/>
+      <c r="O3" s="34"/>
       <c r="Q3" s="6"/>
       <c r="R3" s="6"/>
       <c r="S3" s="6"/>
       <c r="T3" s="5"/>
       <c r="U3" s="5"/>
-      <c r="V3" s="35"/>
-      <c r="W3" s="35"/>
-      <c r="X3" s="35"/>
-      <c r="Y3" s="35"/>
-      <c r="AF3" s="35"/>
-      <c r="AG3" s="35"/>
-      <c r="AH3" s="35"/>
-      <c r="AK3" s="35"/>
-      <c r="AL3" s="35"/>
-      <c r="AM3" s="35"/>
-      <c r="AN3" s="35"/>
-      <c r="AO3" s="35"/>
+      <c r="V3" s="34"/>
+      <c r="W3" s="34"/>
+      <c r="X3" s="34"/>
+      <c r="Y3" s="34"/>
+      <c r="AF3" s="34"/>
+      <c r="AG3" s="34"/>
+      <c r="AH3" s="34"/>
+      <c r="AK3" s="34"/>
+      <c r="AL3" s="34"/>
+      <c r="AM3" s="34"/>
+      <c r="AN3" s="34"/>
+      <c r="AO3" s="34"/>
     </row>
     <row r="4" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A4" s="5"/>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
-      <c r="L4" s="35"/>
-      <c r="M4" s="35"/>
-      <c r="N4" s="35"/>
-      <c r="O4" s="35"/>
+      <c r="L4" s="34"/>
+      <c r="M4" s="34"/>
+      <c r="N4" s="34"/>
+      <c r="O4" s="34"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
       <c r="S4" s="6"/>
       <c r="T4" s="5"/>
       <c r="U4" s="5"/>
-      <c r="V4" s="35"/>
-      <c r="W4" s="35"/>
-      <c r="X4" s="35"/>
-      <c r="Y4" s="35"/>
-      <c r="AF4" s="35"/>
-      <c r="AG4" s="35"/>
-      <c r="AH4" s="35"/>
-      <c r="AK4" s="35"/>
-      <c r="AL4" s="35"/>
-      <c r="AM4" s="35"/>
-      <c r="AN4" s="35"/>
-      <c r="AO4" s="35"/>
+      <c r="V4" s="34"/>
+      <c r="W4" s="34"/>
+      <c r="X4" s="34"/>
+      <c r="Y4" s="34"/>
+      <c r="AF4" s="34"/>
+      <c r="AG4" s="34"/>
+      <c r="AH4" s="34"/>
+      <c r="AK4" s="34"/>
+      <c r="AL4" s="34"/>
+      <c r="AM4" s="34"/>
+      <c r="AN4" s="34"/>
+      <c r="AO4" s="34"/>
     </row>
     <row r="5" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
@@ -3822,22 +3814,22 @@
       <c r="S5" s="6"/>
       <c r="T5" s="6"/>
       <c r="U5" s="6"/>
-      <c r="AF5" s="35"/>
-      <c r="AG5" s="35"/>
-      <c r="AH5" s="35"/>
-      <c r="AK5" s="35"/>
-      <c r="AL5" s="35"/>
-      <c r="AM5" s="35"/>
-      <c r="AN5" s="35"/>
-      <c r="AO5" s="35"/>
+      <c r="AF5" s="34"/>
+      <c r="AG5" s="34"/>
+      <c r="AH5" s="34"/>
+      <c r="AK5" s="34"/>
+      <c r="AL5" s="34"/>
+      <c r="AM5" s="34"/>
+      <c r="AN5" s="34"/>
+      <c r="AO5" s="34"/>
     </row>
     <row r="6" spans="1:46" x14ac:dyDescent="0.25">
-      <c r="A6" s="33" t="s">
+      <c r="A6" s="35" t="s">
         <v>34</v>
       </c>
-      <c r="B6" s="33"/>
-      <c r="C6" s="33"/>
-      <c r="D6" s="33"/>
+      <c r="B6" s="35"/>
+      <c r="C6" s="35"/>
+      <c r="D6" s="35"/>
       <c r="L6" s="4"/>
       <c r="M6" s="5"/>
       <c r="N6" s="5"/>
@@ -3879,63 +3871,63 @@
       <c r="I7" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="L7" s="39"/>
-      <c r="M7" s="37" t="s">
+      <c r="L7" s="3"/>
+      <c r="M7" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="N7" s="37" t="s">
+      <c r="N7" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="O7" s="37" t="s">
+      <c r="O7" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="P7" s="37" t="s">
+      <c r="P7" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="Q7" s="39" t="s">
+      <c r="Q7" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="R7" s="37" t="s">
+      <c r="R7" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="S7" s="37" t="s">
+      <c r="S7" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="T7" s="37" t="s">
+      <c r="T7" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="V7" s="34" t="s">
+      <c r="V7" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="W7" s="34"/>
+      <c r="W7" s="36"/>
       <c r="AC7" s="18"/>
       <c r="AD7" s="18"/>
       <c r="AH7" s="1" t="s">
         <v>12</v>
       </c>
       <c r="AI7" s="9"/>
-      <c r="AL7" s="37" t="s">
+      <c r="AL7" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AM7" s="37" t="s">
+      <c r="AM7" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AN7" s="37" t="s">
+      <c r="AN7" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AO7" s="37" t="s">
+      <c r="AO7" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AP7" s="39" t="s">
+      <c r="AP7" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="AQ7" s="37" t="s">
+      <c r="AQ7" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AR7" s="37" t="s">
+      <c r="AR7" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AS7" s="37" t="s">
+      <c r="AS7" s="1" t="s">
         <v>39</v>
       </c>
       <c r="AT7" s="1" t="s">
@@ -3971,7 +3963,7 @@
       <c r="I8" s="9">
         <v>2</v>
       </c>
-      <c r="L8" s="37" t="s">
+      <c r="L8" s="1" t="s">
         <v>29</v>
       </c>
       <c r="M8" s="9">
@@ -4006,7 +3998,7 @@
         <f t="shared" ref="T8" si="4">I8/I$16</f>
         <v>0.13333333333333333</v>
       </c>
-      <c r="V8" s="37" t="s">
+      <c r="V8" s="1" t="s">
         <v>29</v>
       </c>
       <c r="W8" s="9">
@@ -4097,7 +4089,7 @@
       <c r="I9" s="13">
         <v>2</v>
       </c>
-      <c r="L9" s="37" t="s">
+      <c r="L9" s="1" t="s">
         <v>30</v>
       </c>
       <c r="M9" s="9">
@@ -4132,7 +4124,7 @@
         <f t="shared" ref="T9:T11" si="9">I9/I$16</f>
         <v>0.13333333333333333</v>
       </c>
-      <c r="V9" s="37" t="s">
+      <c r="V9" s="1" t="s">
         <v>30</v>
       </c>
       <c r="W9" s="9">
@@ -4221,7 +4213,7 @@
       <c r="I10" s="13">
         <v>2</v>
       </c>
-      <c r="L10" s="37" t="s">
+      <c r="L10" s="1" t="s">
         <v>31</v>
       </c>
       <c r="M10" s="9">
@@ -4256,7 +4248,7 @@
         <f t="shared" si="9"/>
         <v>0.13333333333333333</v>
       </c>
-      <c r="V10" s="37" t="s">
+      <c r="V10" s="1" t="s">
         <v>31</v>
       </c>
       <c r="W10" s="9">
@@ -4345,7 +4337,7 @@
       <c r="I11" s="13">
         <v>2</v>
       </c>
-      <c r="L11" s="37" t="s">
+      <c r="L11" s="1" t="s">
         <v>35</v>
       </c>
       <c r="M11" s="9">
@@ -4380,7 +4372,7 @@
         <f t="shared" si="9"/>
         <v>0.13333333333333333</v>
       </c>
-      <c r="V11" s="37" t="s">
+      <c r="V11" s="1" t="s">
         <v>35</v>
       </c>
       <c r="W11" s="9">
@@ -4434,7 +4426,7 @@
       <c r="I12" s="13">
         <v>2</v>
       </c>
-      <c r="L12" s="39" t="s">
+      <c r="L12" s="3" t="s">
         <v>36</v>
       </c>
       <c r="M12" s="9">
@@ -4469,7 +4461,7 @@
         <f t="shared" ref="T12:T15" si="24">I12/I$16</f>
         <v>0.13333333333333333</v>
       </c>
-      <c r="V12" s="39" t="s">
+      <c r="V12" s="3" t="s">
         <v>36</v>
       </c>
       <c r="W12" s="9">
@@ -4519,7 +4511,7 @@
       <c r="I13" s="13">
         <v>2</v>
       </c>
-      <c r="L13" s="37" t="s">
+      <c r="L13" s="1" t="s">
         <v>37</v>
       </c>
       <c r="M13" s="9">
@@ -4554,7 +4546,7 @@
         <f t="shared" si="24"/>
         <v>0.13333333333333333</v>
       </c>
-      <c r="V13" s="37" t="s">
+      <c r="V13" s="1" t="s">
         <v>37</v>
       </c>
       <c r="W13" s="9">
@@ -4605,7 +4597,7 @@
       <c r="I14" s="13">
         <v>2</v>
       </c>
-      <c r="L14" s="37" t="s">
+      <c r="L14" s="1" t="s">
         <v>38</v>
       </c>
       <c r="M14" s="9">
@@ -4640,7 +4632,7 @@
         <f t="shared" si="24"/>
         <v>0.13333333333333333</v>
       </c>
-      <c r="V14" s="37" t="s">
+      <c r="V14" s="1" t="s">
         <v>38</v>
       </c>
       <c r="W14" s="9">
@@ -4691,7 +4683,7 @@
         <f t="array" ref="I15">IF(ROW()-ROW($B$8)=COLUMN()-COLUMN($B$8),1,IF(ROW()-ROW($B$8)&gt;COLUMN()-COLUMN($B$8),IFERROR(1/INDEX($B$8:$I$15,COLUMN()-COLUMN($B$8)+1,ROW()-ROW($B$8)+1),""),""))</f>
         <v>1</v>
       </c>
-      <c r="L15" s="37" t="s">
+      <c r="L15" s="1" t="s">
         <v>39</v>
       </c>
       <c r="M15" s="9">
@@ -4726,7 +4718,7 @@
         <f t="shared" si="24"/>
         <v>6.6666666666666666E-2</v>
       </c>
-      <c r="V15" s="37" t="s">
+      <c r="V15" s="1" t="s">
         <v>39</v>
       </c>
       <c r="W15" s="9">
@@ -4737,7 +4729,7 @@
       <c r="AF15" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="AG15" s="36">
+      <c r="AG15" s="33">
         <f>AG13/AG14</f>
         <v>0.19309494745450545</v>
       </c>
@@ -4775,7 +4767,6 @@
         <f t="shared" si="25"/>
         <v>15</v>
       </c>
-      <c r="L16" s="38"/>
       <c r="M16" s="10">
         <f>SUM(M8:M15)</f>
         <v>1.0000000000000002</v>
@@ -4951,11 +4942,11 @@
         <f t="shared" si="27"/>
         <v>0.6</v>
       </c>
-      <c r="W22" s="40" t="s">
+      <c r="W22" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="X22" s="40"/>
-      <c r="Y22" s="40"/>
+      <c r="X22" s="18"/>
+      <c r="Y22" s="18"/>
       <c r="Z22" s="20"/>
       <c r="AG22" s="9" cm="1">
         <f t="array" ref="AG22">SUMPRODUCT($B23:$D23,TRANSPOSE($W$24:$W$26))</f>
@@ -4997,28 +4988,28 @@
         <f t="shared" si="27"/>
         <v>0.1</v>
       </c>
-      <c r="W23" s="37" t="s">
+      <c r="W23" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="X23" s="37" t="s">
+      <c r="X23" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="Y23" s="37" t="s">
+      <c r="Y23" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="Z23" s="37" t="s">
+      <c r="Z23" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AA23" s="39" t="s">
+      <c r="AA23" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="AB23" s="37" t="s">
+      <c r="AB23" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AC23" s="37" t="s">
+      <c r="AC23" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AD23" s="37" t="s">
+      <c r="AD23" s="1" t="s">
         <v>39</v>
       </c>
       <c r="AF23" s="1" t="s">
@@ -5277,7 +5268,7 @@
       <c r="AF27" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="AG27" s="36">
+      <c r="AG27" s="33">
         <f>AG25/AG26</f>
         <v>0.32596666724455747</v>
       </c>
@@ -5662,7 +5653,7 @@
       <c r="AF39" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="AG39" s="36">
+      <c r="AG39" s="33">
         <f>AG37/AG38</f>
         <v>0.44645751409722506</v>
       </c>
@@ -6092,7 +6083,7 @@
       <c r="AF51" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="AG51" s="36">
+      <c r="AG51" s="33">
         <f>AG49/AG50</f>
         <v>0.79254024713630133</v>
       </c>
@@ -6426,7 +6417,7 @@
       <c r="AF62" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="AG62" s="36">
+      <c r="AG62" s="33">
         <f>AG60/AG61</f>
         <v>0.32596666724455747</v>
       </c>
@@ -6645,7 +6636,7 @@
       <c r="AF73" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="AG73" s="36">
+      <c r="AG73" s="33">
         <f>AG71/AG72</f>
         <v>0.44645751409722506</v>
       </c>
@@ -6791,7 +6782,7 @@
       <c r="AF84" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="AG84" s="36">
+      <c r="AG84" s="33">
         <f>AG82/AG83</f>
         <v>0.79254024713630133</v>
       </c>
@@ -6883,7 +6874,7 @@
       <c r="AF95" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="AG95" s="36">
+      <c r="AG95" s="33">
         <f>AG93/AG94</f>
         <v>0.79254024713630133</v>
       </c>
@@ -6899,13 +6890,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="V7:W7"/>
+    <mergeCell ref="A1:D3"/>
     <mergeCell ref="L1:O4"/>
     <mergeCell ref="AF1:AH5"/>
     <mergeCell ref="AK1:AO5"/>
     <mergeCell ref="V1:Y4"/>
     <mergeCell ref="A6:D6"/>
-    <mergeCell ref="V7:W7"/>
-    <mergeCell ref="A1:D3"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
